--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 13:01 UK time</t>
+          <t>2026-10-20 17:06 UK time</t>
         </is>
       </c>
     </row>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="F3" t="n">
-        <v>495.06</v>
+        <v>495.16</v>
       </c>
     </row>
     <row r="4">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>781.3200000000001</v>
+        <v>807</v>
       </c>
       <c r="F4" t="n">
-        <v>588.12</v>
+        <v>588.25</v>
       </c>
     </row>
     <row r="5">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3154</v>
+        <v>3250</v>
       </c>
       <c r="F5" t="n">
-        <v>2494.72</v>
+        <v>2495.2</v>
       </c>
     </row>
     <row r="6">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4896</v>
+        <v>4940</v>
       </c>
       <c r="F6" t="n">
-        <v>4073.06</v>
+        <v>4073.28</v>
       </c>
     </row>
     <row r="7">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1716</v>
+        <v>1754</v>
       </c>
       <c r="F7" t="n">
-        <v>1633.16</v>
+        <v>1633.36</v>
       </c>
     </row>
     <row r="8">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12080</v>
+        <v>12320</v>
       </c>
       <c r="F8" t="n">
-        <v>11216.35</v>
+        <v>11217.55</v>
       </c>
     </row>
     <row r="9">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>693</v>
+        <v>706.5</v>
       </c>
       <c r="F9" t="n">
-        <v>611.6900000000001</v>
+        <v>611.75</v>
       </c>
     </row>
     <row r="10">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>330.4</v>
+        <v>331.2</v>
       </c>
       <c r="F10" t="n">
-        <v>280.45</v>
+        <v>280.46</v>
       </c>
     </row>
     <row r="11">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>251.19</v>
+        <v>252</v>
       </c>
       <c r="F11" t="n">
         <v>201.61</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2014</v>
+        <v>2036</v>
       </c>
       <c r="F12" t="n">
-        <v>1943.93</v>
+        <v>1944.09</v>
       </c>
     </row>
     <row r="13">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>299.8</v>
+        <v>293.2</v>
       </c>
       <c r="F13" t="n">
-        <v>231.66</v>
+        <v>231.63</v>
       </c>
     </row>
     <row r="14">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="F14" t="n">
-        <v>703.95</v>
+        <v>703.98</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Atalaya Mining</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HSBA.L</t>
+          <t>ATYM.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1371.8</v>
+        <v>920.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1368.24</v>
+        <v>890.08</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>AEP Plantations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>AEP.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>156.9</v>
+        <v>174</v>
       </c>
       <c r="F16" t="n">
-        <v>151.75</v>
+        <v>171.4</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GLEN.L</t>
+          <t>HSBA.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>557.8</v>
+        <v>1385.2</v>
       </c>
       <c r="F17" t="n">
-        <v>538.02</v>
+        <v>1368.3</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Funding Circle</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FCH.L</t>
+          <t>MTRO.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="F18" t="n">
-        <v>167.77</v>
+        <v>151.77</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Playtech</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PTEC.L</t>
+          <t>GLEN.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>363.6</v>
+        <v>550</v>
       </c>
       <c r="F19" t="n">
-        <v>355.94</v>
+        <v>537.99</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vodafone Group</t>
+          <t>Raspberry Pi Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VOD.L</t>
+          <t>RPI.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>119.5</v>
+        <v>574</v>
       </c>
       <c r="F20" t="n">
-        <v>113.23</v>
+        <v>572.74</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1365,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle</t>
+          <t>Funding Circle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>FCH.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>563.98</v>
+        <v>206</v>
       </c>
       <c r="F21" t="n">
-        <v>464.68</v>
+        <v>167.82</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Renishaw</t>
+          <t>Playtech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>PTEC.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5200</v>
+        <v>369.2</v>
       </c>
       <c r="F22" t="n">
-        <v>4686.31</v>
+        <v>355.97</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 17:06 UK time</t>
+          <t>2026-10-21 17:06 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-20 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-21 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>246.9%</t>
+          <t>238.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="F3" t="n">
-        <v>495.16</v>
+        <v>497.18</v>
       </c>
     </row>
     <row r="4">
@@ -933,14 +933,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>134.0%</t>
+          <t>130.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="F4" t="n">
-        <v>588.25</v>
+        <v>590.27</v>
       </c>
     </row>
     <row r="5">
@@ -959,14 +959,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>117.9%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3250</v>
+        <v>3192</v>
       </c>
       <c r="F5" t="n">
-        <v>2495.2</v>
+        <v>2502.86</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +985,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4940</v>
+        <v>5120</v>
       </c>
       <c r="F6" t="n">
-        <v>4073.28</v>
+        <v>4083.7</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1754</v>
+        <v>1770</v>
       </c>
       <c r="F7" t="n">
-        <v>1633.36</v>
+        <v>1637.78</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12320</v>
+        <v>12700</v>
       </c>
       <c r="F8" t="n">
-        <v>11217.55</v>
+        <v>11236.49</v>
       </c>
     </row>
     <row r="9">
@@ -1053,24 +1053,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Watches of Switzerland</t>
+          <t>Atalaya Mining</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WOSG.L</t>
+          <t>ATYM.L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>706.5</v>
+        <v>890.5</v>
       </c>
       <c r="F9" t="n">
-        <v>611.75</v>
+        <v>890.2</v>
       </c>
     </row>
     <row r="10">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Watches of Switzerland</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EMG.L</t>
+          <t>WOSG.L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>331.2</v>
+        <v>744</v>
       </c>
       <c r="F10" t="n">
-        <v>280.46</v>
+        <v>613.09</v>
       </c>
     </row>
     <row r="11">
@@ -1105,24 +1105,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Costain Group</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COST.L</t>
+          <t>EMG.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>252</v>
+        <v>327.4</v>
       </c>
       <c r="F11" t="n">
-        <v>201.61</v>
+        <v>280.9</v>
       </c>
     </row>
     <row r="12">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>Costain Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STAN.L</t>
+          <t>COST.L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2036</v>
+        <v>254</v>
       </c>
       <c r="F12" t="n">
-        <v>1944.09</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="13">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ithaca Energy</t>
+          <t>Raspberry Pi Holdings</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>RPI.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>293.2</v>
+        <v>589.5</v>
       </c>
       <c r="F13" t="n">
-        <v>231.63</v>
+        <v>574.21</v>
       </c>
     </row>
     <row r="14">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>STAN.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>910</v>
+        <v>2064</v>
       </c>
       <c r="F14" t="n">
-        <v>703.98</v>
+        <v>1945.74</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atalaya Mining</t>
+          <t>Ithaca Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ATYM.L</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>920.5</v>
+        <v>292.8</v>
       </c>
       <c r="F15" t="n">
-        <v>890.08</v>
+        <v>232.38</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AEP Plantations</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AEP.L</t>
+          <t>GLEN.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>174</v>
+        <v>552.8</v>
       </c>
       <c r="F16" t="n">
-        <v>171.4</v>
+        <v>538.6799999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HSBA.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1385.2</v>
+        <v>916</v>
       </c>
       <c r="F17" t="n">
-        <v>1368.3</v>
+        <v>705.52</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>AEP Plantations</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>AEP.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>161</v>
+        <v>172.4</v>
       </c>
       <c r="F18" t="n">
-        <v>151.77</v>
+        <v>171.57</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GLEN.L</t>
+          <t>HSBA.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>550</v>
+        <v>1398.6</v>
       </c>
       <c r="F19" t="n">
-        <v>537.99</v>
+        <v>1369.56</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Raspberry Pi Holdings</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RPI.L</t>
+          <t>MTRO.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>574</v>
+        <v>164.8</v>
       </c>
       <c r="F20" t="n">
-        <v>572.74</v>
+        <v>151.96</v>
       </c>
     </row>
     <row r="21">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F21" t="n">
-        <v>167.82</v>
+        <v>168.18</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Playtech</t>
+          <t>Renishaw</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PTEC.L</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>369.2</v>
+        <v>5350</v>
       </c>
       <c r="F22" t="n">
-        <v>355.97</v>
+        <v>4694.63</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 17:06 UK time</t>
+          <t>2026-10-21 20:05 UK time</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         <v>2064</v>
       </c>
       <c r="F14" t="n">
-        <v>1945.74</v>
+        <v>1945.73</v>
       </c>
     </row>
     <row r="15">

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 20:05 UK time</t>
+          <t>2026-10-21 22:38 UK time</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         <v>2064</v>
       </c>
       <c r="F14" t="n">
-        <v>1945.73</v>
+        <v>1945.74</v>
       </c>
     </row>
     <row r="15">

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 22:38 UK time</t>
+          <t>2026-10-22 17:08 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-21 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-22 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>238.1%</t>
+          <t>225.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="F3" t="n">
-        <v>497.18</v>
+        <v>499.26</v>
       </c>
     </row>
     <row r="4">
@@ -933,14 +933,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>130.9%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="F4" t="n">
-        <v>590.27</v>
+        <v>592.0700000000001</v>
       </c>
     </row>
     <row r="5">
@@ -959,14 +959,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>117.9%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3192</v>
+        <v>3064</v>
       </c>
       <c r="F5" t="n">
-        <v>2502.86</v>
+        <v>2509.87</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +985,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>103.8%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5120</v>
+        <v>4830</v>
       </c>
       <c r="F6" t="n">
-        <v>4083.7</v>
+        <v>4092.05</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1770</v>
+        <v>1682</v>
       </c>
       <c r="F7" t="n">
-        <v>1637.78</v>
+        <v>1641.71</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12700</v>
+        <v>12150</v>
       </c>
       <c r="F8" t="n">
-        <v>11236.49</v>
+        <v>11252.32</v>
       </c>
     </row>
     <row r="9">
@@ -1053,24 +1053,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Atalaya Mining</t>
+          <t>Watches of Switzerland</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ATYM.L</t>
+          <t>WOSG.L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>890.5</v>
+        <v>741</v>
       </c>
       <c r="F9" t="n">
-        <v>890.2</v>
+        <v>614.38</v>
       </c>
     </row>
     <row r="10">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Watches of Switzerland</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WOSG.L</t>
+          <t>EMG.L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>744</v>
+        <v>319.2</v>
       </c>
       <c r="F10" t="n">
-        <v>613.09</v>
+        <v>281.31</v>
       </c>
     </row>
     <row r="11">
@@ -1105,24 +1105,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Costain Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EMG.L</t>
+          <t>COST.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>327.4</v>
+        <v>248.5</v>
       </c>
       <c r="F11" t="n">
-        <v>280.9</v>
+        <v>202.54</v>
       </c>
     </row>
     <row r="12">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Costain Group</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>COST.L</t>
+          <t>STAN.L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>254</v>
+        <v>1981</v>
       </c>
       <c r="F12" t="n">
-        <v>202.1</v>
+        <v>1946.87</v>
       </c>
     </row>
     <row r="13">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Raspberry Pi Holdings</t>
+          <t>Ithaca Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RPI.L</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>589.5</v>
+        <v>289.6</v>
       </c>
       <c r="F13" t="n">
-        <v>574.21</v>
+        <v>233.12</v>
       </c>
     </row>
     <row r="14">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STAN.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2064</v>
+        <v>898</v>
       </c>
       <c r="F14" t="n">
-        <v>1945.74</v>
+        <v>706.9400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ithaca Energy</t>
+          <t>Renishaw</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>292.8</v>
+        <v>5360</v>
       </c>
       <c r="F15" t="n">
-        <v>232.38</v>
+        <v>4703.28</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GLEN.L</t>
+          <t>MTRO.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>552.8</v>
+        <v>163.4</v>
       </c>
       <c r="F16" t="n">
-        <v>538.6799999999999</v>
+        <v>152.16</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Applied Nutrition</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>APN.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>916</v>
+        <v>292.5</v>
       </c>
       <c r="F17" t="n">
-        <v>705.52</v>
+        <v>267.74</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AEP Plantations</t>
+          <t>Tate &amp; Lyle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AEP.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>172.4</v>
+        <v>563</v>
       </c>
       <c r="F18" t="n">
-        <v>171.57</v>
+        <v>466.78</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Funding Circle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HSBA.L</t>
+          <t>FCH.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1398.6</v>
+        <v>202</v>
       </c>
       <c r="F19" t="n">
-        <v>1369.56</v>
+        <v>168.55</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>164.8</v>
+        <v>2895</v>
       </c>
       <c r="F20" t="n">
-        <v>151.96</v>
+        <v>2644.49</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1365,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Funding Circle</t>
+          <t>4imprint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FCH.L</t>
+          <t>FOUR.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201</v>
+        <v>4372</v>
       </c>
       <c r="F21" t="n">
-        <v>168.18</v>
+        <v>3924.44</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Renishaw</t>
+          <t>Vodafone Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>VOD.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5350</v>
+        <v>119.8</v>
       </c>
       <c r="F22" t="n">
-        <v>4694.63</v>
+        <v>113.41</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 17:08 UK time</t>
+          <t>2026-10-23 17:07 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-22 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-23 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>225.9%</t>
+          <t>213.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>721</v>
+        <v>696</v>
       </c>
       <c r="F3" t="n">
-        <v>499.26</v>
+        <v>501.2</v>
       </c>
     </row>
     <row r="4">
@@ -933,14 +933,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="F4" t="n">
-        <v>592.0700000000001</v>
+        <v>593.91</v>
       </c>
     </row>
     <row r="5">
@@ -959,14 +959,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3064</v>
+        <v>3114</v>
       </c>
       <c r="F5" t="n">
-        <v>2509.87</v>
+        <v>2517.17</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +985,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>103.8%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4830</v>
+        <v>4590</v>
       </c>
       <c r="F6" t="n">
-        <v>4092.05</v>
+        <v>4099.41</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1682</v>
+        <v>1706</v>
       </c>
       <c r="F7" t="n">
-        <v>1641.71</v>
+        <v>1645.64</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12150</v>
+        <v>12060</v>
       </c>
       <c r="F8" t="n">
-        <v>11252.32</v>
+        <v>11267.65</v>
       </c>
     </row>
     <row r="9">
@@ -1063,14 +1063,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="F9" t="n">
-        <v>614.38</v>
+        <v>615.74</v>
       </c>
     </row>
     <row r="10">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Costain Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EMG.L</t>
+          <t>COST.L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>319.2</v>
+        <v>249</v>
       </c>
       <c r="F10" t="n">
-        <v>281.31</v>
+        <v>202.99</v>
       </c>
     </row>
     <row r="11">
@@ -1105,24 +1105,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Costain Group</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COST.L</t>
+          <t>EMG.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248.5</v>
+        <v>313.6</v>
       </c>
       <c r="F11" t="n">
-        <v>202.54</v>
+        <v>281.66</v>
       </c>
     </row>
     <row r="12">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1981</v>
+        <v>1958.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1946.87</v>
+        <v>1947.93</v>
       </c>
     </row>
     <row r="13">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>289.6</v>
+        <v>300.8</v>
       </c>
       <c r="F13" t="n">
-        <v>233.12</v>
+        <v>233.89</v>
       </c>
     </row>
     <row r="14">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Renishaw</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>898</v>
+        <v>5160</v>
       </c>
       <c r="F14" t="n">
-        <v>706.9400000000001</v>
+        <v>4710.61</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Renishaw</t>
+          <t>Applied Nutrition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>APN.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5360</v>
+        <v>294</v>
       </c>
       <c r="F15" t="n">
-        <v>4703.28</v>
+        <v>267.91</v>
       </c>
     </row>
     <row r="16">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>163.4</v>
+        <v>162</v>
       </c>
       <c r="F16" t="n">
-        <v>152.16</v>
+        <v>152.34</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Applied Nutrition</t>
+          <t>Tate &amp; Lyle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>APN.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>292.5</v>
+        <v>564.5</v>
       </c>
       <c r="F17" t="n">
-        <v>267.74</v>
+        <v>467.8</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle</t>
+          <t>Vodafone Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>VOD.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>563</v>
+        <v>118.2</v>
       </c>
       <c r="F18" t="n">
-        <v>466.78</v>
+        <v>113.51</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Funding Circle</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FCH.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>202</v>
+        <v>2855</v>
       </c>
       <c r="F19" t="n">
-        <v>168.55</v>
+        <v>2647.43</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith</t>
+          <t>Helios Towers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>HTWS.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2895</v>
+        <v>207</v>
       </c>
       <c r="F20" t="n">
-        <v>2644.49</v>
+        <v>201.13</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1365,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4imprint</t>
+          <t>Clarkson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FOUR.L</t>
+          <t>CKN.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4372</v>
+        <v>4962</v>
       </c>
       <c r="F21" t="n">
-        <v>3924.44</v>
+        <v>4627.34</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vodafone Group</t>
+          <t>Bodycote</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VOD.L</t>
+          <t>BOY.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>119.8</v>
+        <v>910</v>
       </c>
       <c r="F22" t="n">
-        <v>113.41</v>
+        <v>761.83</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 17:07 UK time</t>
+          <t>2026-10-23 20:16 UK time</t>
         </is>
       </c>
     </row>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 20:16 UK time</t>
+          <t>2026-10-26 17:08 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-23 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-26 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>213.5%</t>
+          <t>224.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="F3" t="n">
-        <v>501.2</v>
+        <v>503.18</v>
       </c>
     </row>
     <row r="4">
@@ -933,14 +933,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>801</v>
+        <v>823</v>
       </c>
       <c r="F4" t="n">
-        <v>593.91</v>
+        <v>595.84</v>
       </c>
     </row>
     <row r="5">
@@ -959,14 +959,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3114</v>
+        <v>3176</v>
       </c>
       <c r="F5" t="n">
-        <v>2517.17</v>
+        <v>2524.87</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +985,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4590</v>
+        <v>5190</v>
       </c>
       <c r="F6" t="n">
-        <v>4099.41</v>
+        <v>4109.67</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="F7" t="n">
-        <v>1645.64</v>
+        <v>1649.58</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12060</v>
+        <v>12260</v>
       </c>
       <c r="F8" t="n">
-        <v>11267.65</v>
+        <v>11283.64</v>
       </c>
     </row>
     <row r="9">
@@ -1063,14 +1063,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>745</v>
+        <v>756.5</v>
       </c>
       <c r="F9" t="n">
-        <v>615.74</v>
+        <v>617.17</v>
       </c>
     </row>
     <row r="10">
@@ -1089,14 +1089,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249</v>
+        <v>259.5</v>
       </c>
       <c r="F10" t="n">
-        <v>202.99</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="11">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>313.6</v>
+        <v>334.4</v>
       </c>
       <c r="F11" t="n">
-        <v>281.66</v>
+        <v>282.11</v>
       </c>
     </row>
     <row r="12">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1958.5</v>
+        <v>2010</v>
       </c>
       <c r="F12" t="n">
-        <v>1947.93</v>
+        <v>1949.09</v>
       </c>
     </row>
     <row r="13">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ithaca Energy</t>
+          <t>Renishaw</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>300.8</v>
+        <v>5375</v>
       </c>
       <c r="F13" t="n">
-        <v>233.89</v>
+        <v>4719.01</v>
       </c>
     </row>
     <row r="14">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Renishaw</t>
+          <t>Applied Nutrition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>APN.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5160</v>
+        <v>295</v>
       </c>
       <c r="F14" t="n">
-        <v>4710.61</v>
+        <v>268.12</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Applied Nutrition</t>
+          <t>Ithaca Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>APN.L</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>294</v>
+        <v>309.8</v>
       </c>
       <c r="F15" t="n">
-        <v>267.91</v>
+        <v>234.69</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>162</v>
+        <v>2905</v>
       </c>
       <c r="F16" t="n">
-        <v>152.34</v>
+        <v>2650.55</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>MTRO.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>564.5</v>
+        <v>167</v>
       </c>
       <c r="F17" t="n">
-        <v>467.8</v>
+        <v>152.55</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vodafone Group</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VOD.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>118.2</v>
+        <v>899</v>
       </c>
       <c r="F18" t="n">
-        <v>113.51</v>
+        <v>709.5599999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith</t>
+          <t>Tate &amp; Lyle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2855</v>
+        <v>565</v>
       </c>
       <c r="F19" t="n">
-        <v>2647.43</v>
+        <v>468.81</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Helios Towers</t>
+          <t>Vodafone Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HTWS.L</t>
+          <t>VOD.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>207</v>
+        <v>118.25</v>
       </c>
       <c r="F20" t="n">
-        <v>201.13</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="21">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4962</v>
+        <v>5095</v>
       </c>
       <c r="F21" t="n">
-        <v>4627.34</v>
+        <v>4632.69</v>
       </c>
     </row>
     <row r="22">
@@ -1401,14 +1401,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F22" t="n">
-        <v>761.83</v>
+        <v>762.8</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 17:08 UK time</t>
+          <t>2026-10-26 20:31 UK time</t>
         </is>
       </c>
     </row>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 20:31 UK time</t>
+          <t>2026-10-26 20:45 UK time</t>
         </is>
       </c>
     </row>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 20:45 UK time</t>
+          <t>2026-10-27 17:07 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-26 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-27 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>224.6%</t>
+          <t>217.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="F3" t="n">
-        <v>503.18</v>
+        <v>505.19</v>
       </c>
     </row>
     <row r="4">
@@ -923,24 +923,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saga</t>
+          <t>Keller Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAGA.L</t>
+          <t>KLR.L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>119.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>823</v>
+        <v>3158</v>
       </c>
       <c r="F4" t="n">
-        <v>595.84</v>
+        <v>2532.59</v>
       </c>
     </row>
     <row r="5">
@@ -949,24 +949,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keller Group</t>
+          <t>Saga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KLR.L</t>
+          <t>SAGA.L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3176</v>
+        <v>850</v>
       </c>
       <c r="F5" t="n">
-        <v>2524.87</v>
+        <v>597.95</v>
       </c>
     </row>
     <row r="6">
@@ -975,24 +975,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Computacenter</t>
+          <t>XP Power</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CCC.L</t>
+          <t>XPP.L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5190</v>
+        <v>1776</v>
       </c>
       <c r="F6" t="n">
-        <v>4109.67</v>
+        <v>1653.88</v>
       </c>
     </row>
     <row r="7">
@@ -1001,24 +1001,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XP Power</t>
+          <t>Computacenter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>XPP.L</t>
+          <t>CCC.L</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1698</v>
+        <v>5250</v>
       </c>
       <c r="F7" t="n">
-        <v>1649.58</v>
+        <v>4120.37</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12260</v>
+        <v>12380</v>
       </c>
       <c r="F8" t="n">
-        <v>11283.64</v>
+        <v>11299.79</v>
       </c>
     </row>
     <row r="9">
@@ -1063,14 +1063,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>756.5</v>
+        <v>731</v>
       </c>
       <c r="F9" t="n">
-        <v>617.17</v>
+        <v>618.46</v>
       </c>
     </row>
     <row r="10">
@@ -1089,14 +1089,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>259.5</v>
+        <v>263.5</v>
       </c>
       <c r="F10" t="n">
-        <v>203.5</v>
+        <v>204.03</v>
       </c>
     </row>
     <row r="11">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>334.4</v>
+        <v>337.6</v>
       </c>
       <c r="F11" t="n">
-        <v>282.11</v>
+        <v>282.57</v>
       </c>
     </row>
     <row r="12">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STAN.L</t>
+          <t>GLEN.L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2010</v>
+        <v>541.8</v>
       </c>
       <c r="F12" t="n">
-        <v>1949.09</v>
+        <v>540.62</v>
       </c>
     </row>
     <row r="13">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Renishaw</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>STAN.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5375</v>
+        <v>2019</v>
       </c>
       <c r="F13" t="n">
-        <v>4719.01</v>
+        <v>1950.26</v>
       </c>
     </row>
     <row r="14">
@@ -1193,14 +1193,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>295</v>
+        <v>294.5</v>
       </c>
       <c r="F14" t="n">
-        <v>268.12</v>
+        <v>268.36</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ithaca Energy</t>
+          <t>Renishaw</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>309.8</v>
+        <v>5520</v>
       </c>
       <c r="F15" t="n">
-        <v>234.69</v>
+        <v>4728.51</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith</t>
+          <t>Ithaca Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2905</v>
+        <v>305.8</v>
       </c>
       <c r="F16" t="n">
-        <v>2650.55</v>
+        <v>235.43</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>167</v>
+        <v>3020</v>
       </c>
       <c r="F17" t="n">
-        <v>152.55</v>
+        <v>2654.37</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Tate &amp; Lyle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>899</v>
+        <v>564</v>
       </c>
       <c r="F18" t="n">
-        <v>709.5599999999999</v>
+        <v>469.81</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle</t>
+          <t>Bodycote</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>BOY.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>565</v>
+        <v>916</v>
       </c>
       <c r="F19" t="n">
-        <v>468.81</v>
+        <v>763.8</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vodafone Group</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VOD.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>118.25</v>
+        <v>911</v>
       </c>
       <c r="F20" t="n">
-        <v>113.6</v>
+        <v>710.95</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1365,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clarkson</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CKN.L</t>
+          <t>MTRO.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5095</v>
+        <v>168.6</v>
       </c>
       <c r="F21" t="n">
-        <v>4632.69</v>
+        <v>152.78</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bodycote</t>
+          <t>EasyJet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOY.L</t>
+          <t>EZJ.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>915</v>
+        <v>680</v>
       </c>
       <c r="F22" t="n">
-        <v>762.8</v>
+        <v>523.46</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 17:07 UK time</t>
+          <t>2026-10-27 21:29 UK time</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v>2019</v>
       </c>
       <c r="F13" t="n">
-        <v>1950.26</v>
+        <v>1950.25</v>
       </c>
     </row>
     <row r="14">

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 21:29 UK time</t>
+          <t>2026-10-27 21:41 UK time</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v>2019</v>
       </c>
       <c r="F13" t="n">
-        <v>1950.25</v>
+        <v>1950.24</v>
       </c>
     </row>
     <row r="14">

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 21:41 UK time</t>
+          <t>2026-10-28 17:08 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-27 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-28 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>217.9%</t>
+          <t>218.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="F3" t="n">
-        <v>505.19</v>
+        <v>507.14</v>
       </c>
     </row>
     <row r="4">
@@ -923,24 +923,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keller Group</t>
+          <t>Saga</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KLR.L</t>
+          <t>SAGA.L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>119.3%</t>
+          <t>137.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3158</v>
+        <v>846</v>
       </c>
       <c r="F4" t="n">
-        <v>2532.59</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="5">
@@ -949,24 +949,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saga</t>
+          <t>Keller Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAGA.L</t>
+          <t>KLR.L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>850</v>
+        <v>3162</v>
       </c>
       <c r="F5" t="n">
-        <v>597.95</v>
+        <v>2540.24</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +985,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1776</v>
+        <v>1790</v>
       </c>
       <c r="F6" t="n">
-        <v>1653.88</v>
+        <v>1658.33</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5250</v>
+        <v>5265</v>
       </c>
       <c r="F7" t="n">
-        <v>4120.37</v>
+        <v>4131.38</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12380</v>
+        <v>12500</v>
       </c>
       <c r="F8" t="n">
-        <v>11299.79</v>
+        <v>11315.49</v>
       </c>
     </row>
     <row r="9">
@@ -1063,14 +1063,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F9" t="n">
-        <v>618.46</v>
+        <v>619.74</v>
       </c>
     </row>
     <row r="10">
@@ -1089,14 +1089,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>263.5</v>
+        <v>259.5</v>
       </c>
       <c r="F10" t="n">
-        <v>204.03</v>
+        <v>204.55</v>
       </c>
     </row>
     <row r="11">
@@ -1105,24 +1105,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Renishaw</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EMG.L</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>337.6</v>
+        <v>5625</v>
       </c>
       <c r="F11" t="n">
-        <v>282.57</v>
+        <v>4738.48</v>
       </c>
     </row>
     <row r="12">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GLEN.L</t>
+          <t>EMG.L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>541.8</v>
+        <v>333</v>
       </c>
       <c r="F12" t="n">
-        <v>540.62</v>
+        <v>282.99</v>
       </c>
     </row>
     <row r="13">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>Applied Nutrition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>STAN.L</t>
+          <t>APN.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2019</v>
+        <v>294.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1950.24</v>
+        <v>268.62</v>
       </c>
     </row>
     <row r="14">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Applied Nutrition</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>APN.L</t>
+          <t>STAN.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>294.5</v>
+        <v>2068</v>
       </c>
       <c r="F14" t="n">
-        <v>268.36</v>
+        <v>1951.68</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Renishaw</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5520</v>
+        <v>3020</v>
       </c>
       <c r="F15" t="n">
-        <v>4728.51</v>
+        <v>2658.19</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ithaca Energy</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>305.8</v>
+        <v>908</v>
       </c>
       <c r="F16" t="n">
-        <v>235.43</v>
+        <v>712.29</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>GLEN.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3020</v>
+        <v>541.5</v>
       </c>
       <c r="F17" t="n">
-        <v>2654.37</v>
+        <v>540.96</v>
       </c>
     </row>
     <row r="18">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>564</v>
       </c>
       <c r="F18" t="n">
-        <v>469.81</v>
+        <v>470.82</v>
       </c>
     </row>
     <row r="19">
@@ -1323,14 +1323,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>916</v>
       </c>
       <c r="F19" t="n">
-        <v>763.8</v>
+        <v>764.76</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Ithaca Energy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>911</v>
+        <v>307.6</v>
       </c>
       <c r="F20" t="n">
-        <v>710.95</v>
+        <v>236.17</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1365,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>EasyJet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>EZJ.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>168.6</v>
+        <v>679.6</v>
       </c>
       <c r="F21" t="n">
-        <v>152.78</v>
+        <v>524.52</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EasyJet</t>
+          <t>Rotork</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EZJ.L</t>
+          <t>ROR.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>680</v>
+        <v>492.8</v>
       </c>
       <c r="F22" t="n">
-        <v>523.46</v>
+        <v>383.29</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 17:08 UK time</t>
+          <t>2026-10-28 20:31 UK time</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         <v>2068</v>
       </c>
       <c r="F14" t="n">
-        <v>1951.68</v>
+        <v>1951.69</v>
       </c>
     </row>
     <row r="15">

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 20:31 UK time</t>
+          <t>2026-10-29 17:07 UK time</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-28 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-29 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +907,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>218.4%</t>
+          <t>223.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="F3" t="n">
-        <v>507.14</v>
+        <v>509.1</v>
       </c>
     </row>
     <row r="4">
@@ -933,14 +933,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>187.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>846</v>
+        <v>898</v>
       </c>
       <c r="F4" t="n">
-        <v>600.08</v>
+        <v>602.49</v>
       </c>
     </row>
     <row r="5">
@@ -959,14 +959,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3162</v>
+        <v>3150</v>
       </c>
       <c r="F5" t="n">
-        <v>2540.24</v>
+        <v>2547.72</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +985,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1790</v>
+        <v>1814</v>
       </c>
       <c r="F6" t="n">
-        <v>1658.33</v>
+        <v>1663.01</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5265</v>
+        <v>5255</v>
       </c>
       <c r="F7" t="n">
-        <v>4131.38</v>
+        <v>4142.1</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12500</v>
+        <v>12720</v>
       </c>
       <c r="F8" t="n">
-        <v>11315.49</v>
+        <v>11332.45</v>
       </c>
     </row>
     <row r="9">
@@ -1063,14 +1063,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>730</v>
+        <v>732.5</v>
       </c>
       <c r="F9" t="n">
-        <v>619.74</v>
+        <v>621.02</v>
       </c>
     </row>
     <row r="10">
@@ -1089,14 +1089,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>259.5</v>
+        <v>258</v>
       </c>
       <c r="F10" t="n">
-        <v>204.55</v>
+        <v>205.04</v>
       </c>
     </row>
     <row r="11">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5625</v>
+        <v>5505</v>
       </c>
       <c r="F11" t="n">
-        <v>4738.48</v>
+        <v>4692.11</v>
       </c>
     </row>
     <row r="12">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>333</v>
+        <v>336.4</v>
       </c>
       <c r="F12" t="n">
-        <v>282.99</v>
+        <v>283.39</v>
       </c>
     </row>
     <row r="13">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Applied Nutrition</t>
+          <t>Oxford Nanopore Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>APN.L</t>
+          <t>ONT.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>294.5</v>
+        <v>233.4</v>
       </c>
       <c r="F13" t="n">
-        <v>268.62</v>
+        <v>141.4</v>
       </c>
     </row>
     <row r="14">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>Applied Nutrition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STAN.L</t>
+          <t>APN.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2068</v>
+        <v>297</v>
       </c>
       <c r="F14" t="n">
-        <v>1951.69</v>
+        <v>268.9</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith</t>
+          <t>RHI Magnesita</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>RHIM.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3020</v>
+        <v>2760</v>
       </c>
       <c r="F15" t="n">
-        <v>2658.19</v>
+        <v>2720.78</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1235,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>908</v>
+        <v>3040</v>
       </c>
       <c r="F16" t="n">
-        <v>712.29</v>
+        <v>2661.74</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GLEN.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>541.5</v>
+        <v>910</v>
       </c>
       <c r="F17" t="n">
-        <v>540.96</v>
+        <v>713.62</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1287,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle</t>
+          <t>Bodycote</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>BOY.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>564</v>
+        <v>916</v>
       </c>
       <c r="F18" t="n">
-        <v>470.82</v>
+        <v>765.64</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1313,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bodycote</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOY.L</t>
+          <t>STAN.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>916</v>
+        <v>2108</v>
       </c>
       <c r="F19" t="n">
-        <v>764.76</v>
+        <v>1953.31</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ithaca Energy</t>
+          <t>Tate &amp; Lyle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>307.6</v>
+        <v>564</v>
       </c>
       <c r="F20" t="n">
-        <v>236.17</v>
+        <v>471.8</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1365,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EasyJet</t>
+          <t>B&amp;M</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EZJ.L</t>
+          <t>BME.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>679.6</v>
+        <v>272.6</v>
       </c>
       <c r="F21" t="n">
-        <v>524.52</v>
+        <v>200.67</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1391,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rotork</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ROR.L</t>
+          <t>MTRO.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>492.8</v>
+        <v>162.8</v>
       </c>
       <c r="F22" t="n">
-        <v>383.29</v>
+        <v>153.13</v>
       </c>
     </row>
   </sheetData>

--- a/ftse_momentum_live.xlsx
+++ b/ftse_momentum_live.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29 17:07 UK time</t>
+          <t>2026-10-30 17:07 UK time</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -772,6 +772,436 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>Costs (£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CMCX.L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CMC Markets</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.1478</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Rank 1 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAGA.L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Saga</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.9306</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rank 2 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KLR.L</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Keller Group</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.1729</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rank 3 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>XPP.L</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>XP Power</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rank 4 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CCC.L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Computacenter</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Rank 5 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WOSG.L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Watches of Switzerland</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7499</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Rank 6 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BGEO.L</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lion Finance Group</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7422</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Rank 7 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>COST.L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Costain Group</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7209</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Rank 8 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RSW.L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Renishaw</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rank 9 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EMG.L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Man Group</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rank 10 by 12-1 month price change</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -855,7 +1285,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>How the model would rank shares on 2026-10-29 (it only trades at month ends)</t>
+          <t>How the model would rank shares on 2026-10-30 (it only trades at month ends)</t>
         </is>
       </c>
     </row>
@@ -907,14 +1337,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>223.3%</t>
+          <t>214.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="F3" t="n">
-        <v>509.1</v>
+        <v>511.01</v>
       </c>
     </row>
     <row r="4">
@@ -933,14 +1363,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>187.2%</t>
+          <t>193.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="F4" t="n">
-        <v>602.49</v>
+        <v>604.79</v>
       </c>
     </row>
     <row r="5">
@@ -959,14 +1389,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3150</v>
+        <v>3184</v>
       </c>
       <c r="F5" t="n">
-        <v>2547.72</v>
+        <v>2555.21</v>
       </c>
     </row>
     <row r="6">
@@ -985,14 +1415,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1814</v>
+        <v>1730</v>
       </c>
       <c r="F6" t="n">
-        <v>1663.01</v>
+        <v>1667.13</v>
       </c>
     </row>
     <row r="7">
@@ -1011,14 +1441,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5255</v>
+        <v>4938</v>
       </c>
       <c r="F7" t="n">
-        <v>4142.1</v>
+        <v>4151.31</v>
       </c>
     </row>
     <row r="8">
@@ -1027,24 +1457,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lion Finance Group</t>
+          <t>Watches of Switzerland</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BGEO.L</t>
+          <t>WOSG.L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12720</v>
+        <v>745</v>
       </c>
       <c r="F8" t="n">
-        <v>11332.45</v>
+        <v>622.29</v>
       </c>
     </row>
     <row r="9">
@@ -1053,24 +1483,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Watches of Switzerland</t>
+          <t>Lion Finance Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WOSG.L</t>
+          <t>BGEO.L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>732.5</v>
+        <v>12030</v>
       </c>
       <c r="F9" t="n">
-        <v>621.02</v>
+        <v>11345.43</v>
       </c>
     </row>
     <row r="10">
@@ -1089,14 +1519,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F10" t="n">
-        <v>205.04</v>
+        <v>205.51</v>
       </c>
     </row>
     <row r="11">
@@ -1115,14 +1545,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5505</v>
+        <v>5330</v>
       </c>
       <c r="F11" t="n">
-        <v>4692.11</v>
+        <v>4699.68</v>
       </c>
     </row>
     <row r="12">
@@ -1141,14 +1571,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>336.4</v>
+        <v>333.2</v>
       </c>
       <c r="F12" t="n">
-        <v>283.39</v>
+        <v>283.75</v>
       </c>
     </row>
     <row r="13">
@@ -1167,14 +1597,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>233.4</v>
+        <v>222.6</v>
       </c>
       <c r="F13" t="n">
-        <v>141.4</v>
+        <v>141.74</v>
       </c>
     </row>
     <row r="14">
@@ -1193,14 +1623,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F14" t="n">
-        <v>268.9</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="15">
@@ -1209,24 +1639,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RHI Magnesita</t>
+          <t>Hill &amp; Smith</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RHIM.L</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2760</v>
+        <v>2965</v>
       </c>
       <c r="F15" t="n">
-        <v>2720.78</v>
+        <v>2665.06</v>
       </c>
     </row>
     <row r="16">
@@ -1235,24 +1665,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith</t>
+          <t>Victrex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3040</v>
+        <v>903</v>
       </c>
       <c r="F16" t="n">
-        <v>2661.74</v>
+        <v>714.92</v>
       </c>
     </row>
     <row r="17">
@@ -1261,24 +1691,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Victrex</t>
+          <t>Bodycote</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>BOY.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>910</v>
+        <v>915.5</v>
       </c>
       <c r="F17" t="n">
-        <v>713.62</v>
+        <v>766.5</v>
       </c>
     </row>
     <row r="18">
@@ -1287,24 +1717,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bodycote</t>
+          <t>Tate &amp; Lyle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOY.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>916</v>
+        <v>563</v>
       </c>
       <c r="F18" t="n">
-        <v>765.64</v>
+        <v>472.77</v>
       </c>
     </row>
     <row r="19">
@@ -1313,24 +1743,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>B&amp;M</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>STAN.L</t>
+          <t>BME.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2108</v>
+        <v>275.4</v>
       </c>
       <c r="F19" t="n">
-        <v>1953.31</v>
+        <v>201.24</v>
       </c>
     </row>
     <row r="20">
@@ -1339,24 +1769,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>STAN.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>564</v>
+        <v>2055</v>
       </c>
       <c r="F20" t="n">
-        <v>471.8</v>
+        <v>1954.51</v>
       </c>
     </row>
     <row r="21">
@@ -1365,24 +1795,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B&amp;M</t>
+          <t>Rotork</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BME.L</t>
+          <t>ROR.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>272.6</v>
+        <v>494</v>
       </c>
       <c r="F21" t="n">
-        <v>200.67</v>
+        <v>384.85</v>
       </c>
     </row>
     <row r="22">
@@ -1391,24 +1821,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>discoverIE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MTRO.L</t>
+          <t>DSCV.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>162.8</v>
+        <v>826</v>
       </c>
       <c r="F22" t="n">
-        <v>153.13</v>
+        <v>699.5599999999999</v>
       </c>
     </row>
   </sheetData>
